--- a/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
+++ b/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
@@ -504,13 +504,13 @@
         <v>3.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.154</v>
+        <v>0.223</v>
       </c>
       <c r="G2" t="n">
-        <v>246944</v>
+        <v>226911</v>
       </c>
       <c r="H2" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
@@ -532,13 +532,13 @@
         <v>3.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.154</v>
+        <v>0.223</v>
       </c>
       <c r="G3" t="n">
-        <v>33372</v>
+        <v>30664</v>
       </c>
       <c r="H3" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="4">
@@ -560,13 +560,13 @@
         <v>7.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.154</v>
+        <v>0.223</v>
       </c>
       <c r="G4" t="n">
-        <v>39626</v>
+        <v>36411</v>
       </c>
       <c r="H4" t="n">
-        <v>6.28</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="5">
@@ -588,13 +588,13 @@
         <v>3.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.154</v>
+        <v>0.223</v>
       </c>
       <c r="G5" t="n">
-        <v>8116</v>
+        <v>7458</v>
       </c>
       <c r="H5" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="6">
@@ -616,13 +616,13 @@
         <v>3.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.154</v>
+        <v>0.223</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>328058</v>
+        <v>301444</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -778,14 +778,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sur-versement au verre (~8 %)</t>
+          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>446</v>
+        <v>807</v>
       </c>
       <c r="C8" t="n">
-        <v>0.042</v>
+        <v>0.076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -796,48 +796,102 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Degustation offerte (pichet + vin nomme au verre)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>113</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cremant jete en fin de journee (eventé)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>126</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>129</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Stock final (inventaire)</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B12" t="n">
         <v>213</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C12" t="n">
         <v>0.02</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TOTAL conso + stock</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>8203</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>8932</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Achats d'alcool (référence)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>10622</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
+++ b/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
@@ -504,13 +504,13 @@
         <v>3.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G2" t="n">
-        <v>226911</v>
+        <v>226553</v>
       </c>
       <c r="H2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="3">
@@ -532,10 +532,10 @@
         <v>3.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G3" t="n">
-        <v>30664</v>
+        <v>30616</v>
       </c>
       <c r="H3" t="n">
         <v>2.97</v>
@@ -560,13 +560,13 @@
         <v>7.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G4" t="n">
-        <v>36411</v>
+        <v>36354</v>
       </c>
       <c r="H4" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="5">
@@ -588,10 +588,10 @@
         <v>3.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G5" t="n">
-        <v>7458</v>
+        <v>7446</v>
       </c>
       <c r="H5" t="n">
         <v>3.08</v>
@@ -616,13 +616,13 @@
         <v>3.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>301444</v>
+        <v>300969</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
     </row>
   </sheetData>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>8932</v>
+        <v>8945</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
     </row>

--- a/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
+++ b/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
@@ -504,13 +504,13 @@
         <v>3.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.224</v>
+        <v>0.26</v>
       </c>
       <c r="G2" t="n">
-        <v>226553</v>
+        <v>215973</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -532,13 +532,13 @@
         <v>3.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.224</v>
+        <v>0.26</v>
       </c>
       <c r="G3" t="n">
-        <v>30616</v>
+        <v>29186</v>
       </c>
       <c r="H3" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="4">
@@ -560,13 +560,13 @@
         <v>7.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.224</v>
+        <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>36354</v>
+        <v>34656</v>
       </c>
       <c r="H4" t="n">
-        <v>5.76</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5">
@@ -588,13 +588,13 @@
         <v>3.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.224</v>
+        <v>0.26</v>
       </c>
       <c r="G5" t="n">
-        <v>7446</v>
+        <v>7098</v>
       </c>
       <c r="H5" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="6">
@@ -616,13 +616,13 @@
         <v>3.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.224</v>
+        <v>0.26</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>300969</v>
+        <v>286914</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -778,14 +778,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
+          <t>Sur-versement vins/spiritueux/cocktails (free-pour : Kerr 2008, Wansink 2005)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>807</v>
+        <v>1058</v>
       </c>
       <c r="C8" t="n">
-        <v>0.076</v>
+        <v>0.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Degustation offerte (pichet + vin nomme au verre)</t>
+          <t>Degustation offerte (note par note, annexe C)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="C10" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -832,14 +832,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+          <t>Cremant sur-versé (free-pour +23,6 %)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -850,48 +850,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>129</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Stock final (inventaire)</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>213</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>0.02</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL conso + stock</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>8945</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>TOTAL conso + stock</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9417</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Achats d'alcool (référence)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>10622</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
+++ b/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
@@ -504,13 +504,13 @@
         <v>3.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.26</v>
+        <v>0.362</v>
       </c>
       <c r="G2" t="n">
-        <v>215973</v>
+        <v>186321</v>
       </c>
       <c r="H2" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="3">
@@ -532,13 +532,13 @@
         <v>3.83</v>
       </c>
       <c r="F3" t="n">
-        <v>0.26</v>
+        <v>0.362</v>
       </c>
       <c r="G3" t="n">
-        <v>29186</v>
+        <v>25179</v>
       </c>
       <c r="H3" t="n">
-        <v>2.83</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
@@ -560,13 +560,13 @@
         <v>7.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.26</v>
+        <v>0.362</v>
       </c>
       <c r="G4" t="n">
-        <v>34656</v>
+        <v>29898</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="5">
@@ -588,13 +588,13 @@
         <v>3.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.26</v>
+        <v>0.362</v>
       </c>
       <c r="G5" t="n">
-        <v>7098</v>
+        <v>6124</v>
       </c>
       <c r="H5" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -616,13 +616,13 @@
         <v>3.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.26</v>
+        <v>0.362</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>286914</v>
+        <v>247522</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1058</v>
+        <v>720</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>0.068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9417</v>
+        <v>9079</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.887</v>
+        <v>0.855</v>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
     </row>

--- a/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
+++ b/public/documents/pieces-defense/RF-coefficients-de-revente.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coefficient par famille" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cascade des volumes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coef par produit (3 exos)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coef par categorie (3 exos)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ventes par format (3 exos)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Alcool revendu vs non revendu" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Coef declare vs reconstitue" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +32,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,12 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,199 +429,2663 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Famille</t>
+          <t>Produit (caisse)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Litres achetés</t>
+          <t>Categorie</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Achat (€)</t>
+          <t>Format servi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CA théorique au prix carte (€)</t>
+          <t>Nb ventes 3 ans</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient brut</t>
+          <t>Prix de vente moyen</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Part non revendue au verre</t>
+          <t>Prix d'achat matiere</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CA effectif (€)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Coefficient effectif</t>
+          <t>Coefficient</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vins et pétillants</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6539.6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>82550</v>
+          <t>Savagnin verre</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>291903</v>
+        <v>1544</v>
       </c>
       <c r="E2" t="n">
-        <v>3.54</v>
+        <v>7.83</v>
       </c>
       <c r="F2" t="n">
-        <v>0.362</v>
+        <v>2.33</v>
       </c>
       <c r="G2" t="n">
-        <v>186321</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.26</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bière</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2473.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10309</v>
+          <t>pression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>39447</v>
+        <v>2233.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.362</v>
+        <v>0.12</v>
       </c>
       <c r="G3" t="n">
-        <v>25179</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.44</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spiritueux, liqueurs et apéritifs</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>369.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6306</v>
+          <t>Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>46841</v>
+        <v>238</v>
       </c>
       <c r="E4" t="n">
-        <v>7.43</v>
+        <v>33.69</v>
       </c>
       <c r="F4" t="n">
-        <v>0.362</v>
+        <v>10.05</v>
       </c>
       <c r="G4" t="n">
-        <v>29898</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.74</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1/2 Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Demi-bouteille 37.5 cl</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PICHET SAVAGNIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>254</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pinte</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>877</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>31.74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PiCHET TROUSSEAU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>251</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saint Véran Verre</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>819.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Macvin du Jura</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Macvin (vin de liqueur)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Verre 6 cl</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1091.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau Le</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>868</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau Bou</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Beaujolais Moulin à</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>375</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C du Rhone St  Josep</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vin jaune</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vins (autres)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Verre 12 cl</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>312</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crémant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Verre 10 cl</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>810</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>H.C.B BEAUNE BTL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E19" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PICHET SAINT VERAN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>110</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PICHET ALIGOTE 50cL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>315</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H.C.DE BEAUNE  VERRE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>368</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C du  Rhone St Josep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PICHET C.DE BEAUNE B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>265</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Blanche des plateaux</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cidre Bouché Brut</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Cidres</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>548.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2418</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9594</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>167</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ambrée</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>33 cl</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>387</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pichet Saint Joseph</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>81</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Clair de Rosé</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PICHET MOULIN A VENT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>95</v>
+      </c>
+      <c r="E30" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cidre Bouché Doux</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cidres</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MACON VERRE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>320.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PICHET ROSE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G34" t="n">
         <v>3.97</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6124</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL alcool</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>9930.6</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>101584</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>387785</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>247522</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>2.44</v>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Gewurztraminer Le ve</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VIN PAILLE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vins (autres)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Verre 6 cl</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>279.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MACON bouteille</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>62</v>
+      </c>
+      <c r="E37" t="n">
+        <v>31</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PICHET MACON</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PICHET HCB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>56</v>
+      </c>
+      <c r="E39" t="n">
+        <v>32</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Picon bière</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G40" t="n">
+        <v>37.53</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cidre la Mordue</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cidres</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>27 cl</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pinte Picon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G42" t="n">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Panaché</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Pichet CdR CHUSCLAN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Verre ALIGOTE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>345</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Pontarlier</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Verre 2 cl</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chablis Le Verre</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>148</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Verre Rosé</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>291</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Alsace Gewurztramine</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>31</v>
+      </c>
+      <c r="E49" t="n">
+        <v>35</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Verre 2 cl</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>260</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G50" t="n">
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PICHET C.DE BEAUNE R</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>70</v>
+      </c>
+      <c r="E51" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DOMAINE LE PIVE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>35</v>
+      </c>
+      <c r="E52" t="n">
+        <v>29</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Verre 6 cl</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G53" t="n">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Pastis</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Verre 2 cl</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>216</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G54" t="n">
+        <v>12.16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pichet Chablis</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>28</v>
+      </c>
+      <c r="E55" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Vins (autres)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Verre 6 cl</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>135</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>25 cl</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G57" t="n">
+        <v>33.17</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PICHET GEWURZTRAMINE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Pichet 50 cl</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>27</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Verre 6 cl</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Bohème</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>20</v>
+      </c>
+      <c r="E60" t="n">
+        <v>29</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spiritueux</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G61" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Crémant du Jura</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Whisky L.J (4cl)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Spiritueux</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Crément du Jura</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14</v>
+      </c>
+      <c r="E64" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="F64" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>58</v>
+      </c>
+      <c r="E65" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Marc du Jura (4cl)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>60</v>
+      </c>
+      <c r="E66" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MIRAVAL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" t="n">
+        <v>45</v>
+      </c>
+      <c r="F67" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>55</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VERRE H.C.DE BEAUNE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>41</v>
+      </c>
+      <c r="E69" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>H.C.BEAUNE BOUTEILLE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BORD.  MOUTON CADET</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="F71" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GASCOGNE Gd PAVOIS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13</v>
+      </c>
+      <c r="E72" t="n">
+        <v>22</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>43</v>
+      </c>
+      <c r="E73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G73" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Calvados (4cl)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>32</v>
+      </c>
+      <c r="E74" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>34</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BAILEYS</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>33</v>
+      </c>
+      <c r="E76" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G76" t="n">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Baileys</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>33</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G77" t="n">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Eau de vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>28</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VERRE ROSE/PICHET C.DE BEAUNE R</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Verre 15 cl</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>42</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>"Champagne Brut "</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>37</v>
+      </c>
+      <c r="F80" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cognac (4cl)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>23</v>
+      </c>
+      <c r="E81" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Eau de vie Framboise</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>21</v>
+      </c>
+      <c r="E82" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G82" t="n">
+        <v>25.93</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>H.COTES DE NUITS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>GRAND MARNIER</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>17</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>17</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Crémant Rosé</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bouteille 75 cl</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>26</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Vieux Marc Bourgogne</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G87" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Whisky L.J (2cl) Bab</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Spiritueux</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Verre 2 cl</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G88" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G89" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Crément / Jura VERRE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Verre 10 cl</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Spiritueux</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Verre 4 cl</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -636,13 +3099,977 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Categorie</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nb produits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>CA TTC (3 ans)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient (CA / cout matiere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vins blancs</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>73617</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Vins rouges</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47066</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26534</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vins rosés</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7623</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vins (autres)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6520</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cidres</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6264</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Macvin (vin de liqueur)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6067</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pétillants / crémant</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4825</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Apéritifs</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4645</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Liqueurs</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1508</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Eaux-de-vie</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1351</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Spiritueux</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Categorie</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nb ventes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prix moyen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fourchette de prix (saison)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CA TTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Apéritifs MAISON</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6259.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1,10  a 9,30</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>34554</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Vins Blancs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>799</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>19,75  a 75,00</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>26925</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vins Blancs</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Verre</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2832</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2,00  a 8,30</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>21731</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bière (pression)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3273</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2,10  a 9,00</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vins Blancs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pichet (50 cl)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,50  a 32,70</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>16789</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vins Rouges</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pichet (50 cl)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>553</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3,90  a 32,20</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>14185</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vins Rouges</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1601.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,00  a 38,00</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>14048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vins Rouges</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>366</v>
+      </c>
+      <c r="D9" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,00  a 49,00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>13967</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Spécialités Régionales</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2115.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3,40  a 72,00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>13775</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PICHETS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pichet (50 cl)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1197.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,20  a 13,40</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bières</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1529.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3,60  a 8,40</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>8337</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vins Blancs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Demi-bouteille</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19,00  a 24,00</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7550</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pétillants</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9,20  a 60,00</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6424</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Autres Apéritifs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3,20  a 13,00</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Autres Apéritifs</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1368.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3,80  a 4,20</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5715</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COCKTAÏLS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>601.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7,20  a 11,60</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5342</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pétillants</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1152.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3,80  a 7,60</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AUTRES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>583</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4,30  a 9,00</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vins Rosés</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>18,00  a 45,00</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vins Rouges</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verre</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>409</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7,90  a 9,50</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pichet (50 cl)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>315</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5,25  a 10,50</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Digestifs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>515</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4,00  a 11,00</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0307</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Verre</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>636</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3,90  a 4,25</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PICHETS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Verre</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2,00  a 4,50</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Vins Blancs</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Verre / cocktail</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>7,00</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bouteille</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>29,00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,253 +4090,210 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Revendu au verre au prix carte ?</t>
+          <t>Cout d'achat (EUR)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vendu au verre (caisse)</t>
+          <t>Alcool achete (total)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5569</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>10622</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>107924</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vendu en cocktails (caisse, biere des cocktails incluse)</t>
+          <t>Revendu au verre + cocktails</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>998</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
+        <v>6567</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>62 %</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>66723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cuisine (fondues, babas, flambage)</t>
+          <t>NON revendu (cuisine, sur-versement, pertes)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
+        <v>3842</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>36 %</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alcool des menus (non detaille en caisse)</t>
+          <t>Stock final</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
+        <v>213</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2 %</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consommation du chef (Picon + Macvin)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>143</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
+          <t>CA alcool encaisse (caisse, 3 exos)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>257210</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aperitifs offerts aux clients</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>40</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sur-versement vins/spiritueux/cocktails (free-pour : Kerr 2008, Wansink 2005)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>720</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Degustation offerte (note par note, annexe C)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>126</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cremant jete en fin de journee (eventé)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>260</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cremant sur-versé (free-pour +23,6 %)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>87</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Freinte technique de la biere pression (mousse, lignes)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>129</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stock final (inventaire)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>213</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL conso + stock</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>9079</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Achats d'alcool (référence)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>10622</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>COEFFICIENT sur alcool REVENDU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CA declare TTC</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cout matieres</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Coef declare</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Coef apres reconstitution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>404031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>175437</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.404</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>438658</v>
+      </c>
+      <c r="C3" t="n">
+        <v>183693</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.144</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>435525</v>
+      </c>
+      <c r="C4" t="n">
+        <v>188539</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.051</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
